--- a/source_data/workbooks/Source_Data_Fig4.xlsx
+++ b/source_data/workbooks/Source_Data_Fig4.xlsx
@@ -103,10 +103,10 @@
     <t>NOVA</t>
   </si>
   <si>
-    <t>TLAgent</t>
-  </si>
-  <si>
-    <t>reference</t>
+    <t>TissueLab</t>
+  </si>
+  <si>
+    <t>Ground truth</t>
   </si>
   <si>
     <t>accuracy of the answer</t>
